--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T05:10:08+00:00</t>
+    <t>2026-09-03T05:17:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T05:17:43+00:00</t>
+    <t>2026-09-03T05:48:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T05:48:26+00:00</t>
+    <t>2026-09-03T10:47:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T10:47:18+00:00</t>
+    <t>2026-09-08T14:02:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-alpha.6</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T14:02:02+00:00</t>
+    <t>2026-09-09T10:10:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T10:10:08+00:00</t>
+    <t>2026-09-09T13:56:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T13:56:56+00:00</t>
+    <t>2026-09-09T14:11:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T14:11:38+00:00</t>
+    <t>2026-09-09T14:19:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T14:19:13+00:00</t>
+    <t>2026-09-09T14:42:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T14:42:29+00:00</t>
+    <t>2026-09-09T15:55:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
@@ -8,13 +8,14 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
-    <sheet name="Exclude #1" r:id="rId5" sheetId="3"/>
+    <sheet name="Include #1" r:id="rId5" sheetId="3"/>
+    <sheet name="Exclude #2" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="58">
   <si>
     <t>Property</t>
   </si>
@@ -61,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T15:55:32+00:00</t>
+    <t>2026-09-10T12:50:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -134,6 +135,54 @@
   </si>
   <si>
     <t>Concept</t>
+  </si>
+  <si>
+    <t>86930-5</t>
+  </si>
+  <si>
+    <t>Carbapenemase [Presence] in Isolate</t>
+  </si>
+  <si>
+    <t>101673-2</t>
+  </si>
+  <si>
+    <t>KPC carbapenemase [Presence] in Isolate by Rapid immunoassay</t>
+  </si>
+  <si>
+    <t>101675-7</t>
+  </si>
+  <si>
+    <t>IMP Carbapenemase [Presence] in Isolate by Rapid immunoassay</t>
+  </si>
+  <si>
+    <t>101677-3</t>
+  </si>
+  <si>
+    <t>NDM Carbapenemase [Presence] in Isolate by Rapid immunoassay</t>
+  </si>
+  <si>
+    <t>101676-5</t>
+  </si>
+  <si>
+    <t>VIM Carbapenemase [Presence] in Isolate by Rapid immunoassay</t>
+  </si>
+  <si>
+    <t>101674-0</t>
+  </si>
+  <si>
+    <t>OXA-48-like carbapenemase [Presence] in Isolate by Rapid immunoassay</t>
+  </si>
+  <si>
+    <t>92246-8</t>
+  </si>
+  <si>
+    <t>Microorganism resistance mutation detected [Presence] by Molecular method</t>
+  </si>
+  <si>
+    <t>108153-8</t>
+  </si>
+  <si>
+    <t>Genetic determinants of antimicrobial resistance [Presence] in Specimen by NAA with non-probe detection</t>
   </si>
   <si>
     <t>35492-8</t>
@@ -477,7 +526,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -502,17 +551,119 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>36</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
         <v>37</v>
       </c>
+      <c r="B9" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>39</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>56</v>
+      </c>
       <c r="B4" t="s" s="2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>38</v>
       </c>
     </row>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T12:50:06+00:00</t>
+    <t>2026-09-10T13:10:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:10:47+00:00</t>
+    <t>2026-09-10T13:32:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:32:54+00:00</t>
+    <t>2026-09-10T13:47:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:47:44+00:00</t>
+    <t>2026-09-10T16:40:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T16:40:19+00:00</t>
+    <t>2026-09-10T17:22:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T17:22:53+00:00</t>
+    <t>2026-09-10T17:39:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T17:39:40+00:00</t>
+    <t>2026-09-10T18:06:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T18:06:33+00:00</t>
+    <t>2026-09-11T06:33:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T06:33:50+00:00</t>
+    <t>2026-09-11T11:07:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T11:07:28+00:00</t>
+    <t>2026-09-11T11:48:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T11:48:22+00:00</t>
+    <t>2026-09-11T12:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T12:41:50+00:00</t>
+    <t>2026-09-11T12:56:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T12:56:10+00:00</t>
+    <t>2026-09-12T16:17:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T16:17:49+00:00</t>
+    <t>2026-09-12T17:15:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T17:15:10+00:00</t>
+    <t>2026-09-12T20:14:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
